--- a/data/trans_bre/P20-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P20-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,98</t>
+          <t>1,52; 6,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,28</t>
+          <t>1,58; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,13</t>
+          <t>2,44; 9,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,64</t>
+          <t>3,47; 11,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,52; 601,94</t>
+          <t>34,61; 496,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 385,13</t>
+          <t>27,05; 361,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,66; 503,25</t>
+          <t>51,0; 531,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,95</t>
+          <t>5,85; 11,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,11</t>
+          <t>6,81; 13,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,77</t>
+          <t>5,66; 11,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,3</t>
+          <t>-0,5; 7,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>123,69; 521,92</t>
+          <t>130,24; 497,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,02; 386,6</t>
+          <t>121,14; 399,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>169,96; 957,26</t>
+          <t>156,53; 817,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 372,44</t>
+          <t>-11,01; 352,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,36</t>
+          <t>-0,11; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,34</t>
+          <t>-0,1; 5,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,0</t>
+          <t>1,75; 6,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,22</t>
+          <t>-0,25; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 241,05</t>
+          <t>-9,04; 204,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 124,86</t>
+          <t>-3,36; 133,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 290,5</t>
+          <t>33,85; 274,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 186,11</t>
+          <t>-5,92; 183,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,29</t>
+          <t>-2,02; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,82</t>
+          <t>0,08; 5,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,63</t>
+          <t>-0,7; 3,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,07</t>
+          <t>-2,86; 2,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 110,08</t>
+          <t>-37,5; 98,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 135,2</t>
+          <t>0,08; 143,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 143,16</t>
+          <t>-16,64; 147,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 154,6</t>
+          <t>-45,17; 123,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,27</t>
+          <t>-2,02; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,76</t>
+          <t>-2,81; 3,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,05</t>
+          <t>-5,29; 1,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,47</t>
+          <t>-5,73; -0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 117,11</t>
+          <t>-33,44; 129,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 82,38</t>
+          <t>-33,37; 87,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,33; 21,1</t>
+          <t>-58,98; 22,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,75; -5,9</t>
+          <t>-56,77; -4,33</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 4,86</t>
+          <t>-3,6; 4,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,52</t>
+          <t>-4,8; 4,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 1,35</t>
+          <t>-7,92; 1,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -2,71</t>
+          <t>-10,18; -2,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 94,72</t>
+          <t>-35,2; 82,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 66,05</t>
+          <t>-39,22; 64,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 18,76</t>
+          <t>-57,53; 19,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,72; -33,5</t>
+          <t>-84,39; -33,09</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 5,74</t>
+          <t>-4,79; 5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 2,58</t>
+          <t>-9,11; 2,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 6,52</t>
+          <t>-3,07; 6,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,25</t>
+          <t>-5,01; 1,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 88,24</t>
+          <t>-39,39; 91,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 25,8</t>
+          <t>-48,31; 21,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 101,84</t>
+          <t>-29,27; 105,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 26,99</t>
+          <t>-38,16; 24,26</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,51</t>
+          <t>2,26; 4,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,7</t>
+          <t>2,15; 4,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,06</t>
+          <t>1,82; 4,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,87</t>
+          <t>-0,91; 2,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,27; 120,95</t>
+          <t>45,69; 120,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,09; 87,22</t>
+          <t>32,05; 84,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,15; 95,6</t>
+          <t>33,56; 97,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 41,27</t>
+          <t>-14,87; 46,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P20-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1842,5%</t>
+          <t>2159,51%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,59</t>
+          <t>1,6; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,25</t>
+          <t>1,95; 8,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,27</t>
+          <t>2,5; 9,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,88</t>
+          <t>3,43; 12,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,61; 496,59</t>
+          <t>39,49; 580,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,05; 361,12</t>
+          <t>40,24; 360,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,0; 531,6</t>
+          <t>53,65; 485,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104,74%</t>
+          <t>140,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 11,68</t>
+          <t>5,95; 11,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,26</t>
+          <t>6,57; 13,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,61</t>
+          <t>5,86; 11,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,23</t>
+          <t>1,19; 8,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>130,24; 497,41</t>
+          <t>136,58; 515,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>121,14; 399,33</t>
+          <t>110,59; 382,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>156,53; 817,25</t>
+          <t>167,16; 970,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 352,19</t>
+          <t>6,4; 375,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,22</t>
+          <t>0,06; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,58</t>
+          <t>-0,41; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,92</t>
+          <t>1,71; 6,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,93</t>
+          <t>0,38; 5,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 204,76</t>
+          <t>0,82; 217,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 133,51</t>
+          <t>-7,42; 133,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 274,62</t>
+          <t>32,05; 268,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 183,17</t>
+          <t>7,26; 200,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>-27,27%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,15</t>
+          <t>-1,94; 3,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,89</t>
+          <t>0,01; 6,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,76</t>
+          <t>-0,92; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,79</t>
+          <t>-3,98; 0,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 98,32</t>
+          <t>-34,39; 112,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 143,33</t>
+          <t>-1,09; 140,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 147,57</t>
+          <t>-20,65; 154,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 123,77</t>
+          <t>-52,12; 13,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-35,78%</t>
+          <t>-33,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,55</t>
+          <t>-1,98; 4,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,9</t>
+          <t>-3,21; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,1</t>
+          <t>-5,23; 1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -0,43</t>
+          <t>-5,21; -0,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 129,78</t>
+          <t>-33,21; 117,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 87,79</t>
+          <t>-40,23; 72,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,98; 22,44</t>
+          <t>-58,16; 28,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,77; -4,33</t>
+          <t>-53,54; -5,22</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,9</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-61,64%</t>
+          <t>-37,23%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,74</t>
+          <t>-3,74; 4,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,44</t>
+          <t>-5,21; 4,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 1,33</t>
+          <t>-8,13; 0,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -2,87</t>
+          <t>-6,64; -0,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 82,59</t>
+          <t>-38,16; 82,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 64,8</t>
+          <t>-42,52; 61,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,53; 19,69</t>
+          <t>-57,8; 11,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,39; -33,09</t>
+          <t>-57,4; -11,76</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-11,71%</t>
+          <t>-9,96%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,42</t>
+          <t>-4,84; 5,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 2,45</t>
+          <t>-9,18; 2,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,5</t>
+          <t>-3,3; 6,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,98</t>
+          <t>-4,53; 2,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 91,75</t>
+          <t>-39,35; 80,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 21,7</t>
+          <t>-49,58; 19,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 105,69</t>
+          <t>-29,53; 106,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 24,26</t>
+          <t>-35,51; 26,56</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,46</t>
+          <t>2,04; 4,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,76</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,23</t>
+          <t>1,66; 4,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,02</t>
+          <t>-0,26; 1,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,69; 120,31</t>
+          <t>44,22; 120,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,05; 84,73</t>
+          <t>31,37; 87,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,56; 97,41</t>
+          <t>30,11; 93,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 46,87</t>
+          <t>-4,07; 34,6</t>
         </is>
       </c>
     </row>
